--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125497046</v>
+        <v>125494284</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blånk, Blånk, Dlr</t>
+          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501323</v>
+        <v>501195</v>
       </c>
       <c r="R3" t="n">
-        <v>6698299</v>
+        <v>6698498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125493235</v>
+        <v>125493171</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,17 +942,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501131</v>
+        <v>501140</v>
       </c>
       <c r="R4" t="n">
-        <v>6698334</v>
+        <v>6698315</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125494284</v>
+        <v>125494917</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1047,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501195</v>
+        <v>501144</v>
       </c>
       <c r="R5" t="n">
-        <v>6698498</v>
+        <v>6698592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,11 +1135,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125493171</v>
+        <v>125494588</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,52 +1173,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blånk, Blånk, Dlr</t>
+          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501140</v>
+        <v>501130</v>
       </c>
       <c r="R6" t="n">
-        <v>6698315</v>
+        <v>6698527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125494588</v>
+        <v>125495484</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,27 +1299,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,10 +1332,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501130</v>
+        <v>501295</v>
       </c>
       <c r="R7" t="n">
-        <v>6698527</v>
+        <v>6698542</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125494917</v>
+        <v>125492793</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,52 +1416,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
+          <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501144</v>
+        <v>501287</v>
       </c>
       <c r="R8" t="n">
-        <v>6698592</v>
+        <v>6698230</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1489,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125495484</v>
+        <v>125497046</v>
       </c>
       <c r="B9" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,43 +1537,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
+          <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501295</v>
+        <v>501323</v>
       </c>
       <c r="R9" t="n">
-        <v>6698542</v>
+        <v>6698299</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125492793</v>
+        <v>125493235</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,25 +1655,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1678,10 +1683,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501287</v>
+        <v>501131</v>
       </c>
       <c r="R10" t="n">
-        <v>6698230</v>
+        <v>6698334</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1723,12 +1728,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125495038</v>
+        <v>125492793</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
+          <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501202</v>
+        <v>501287</v>
       </c>
       <c r="R2" t="n">
-        <v>6698589</v>
+        <v>6698230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125494284</v>
+        <v>125495484</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501195</v>
+        <v>501295</v>
       </c>
       <c r="R3" t="n">
-        <v>6698498</v>
+        <v>6698542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1035,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125494917</v>
+        <v>125493235</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
@@ -1068,31 +1072,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
+          <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501144</v>
+        <v>501131</v>
       </c>
       <c r="R5" t="n">
-        <v>6698592</v>
+        <v>6698334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125494588</v>
+        <v>125497991</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,39 +1167,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
+          <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501130</v>
+        <v>501259</v>
       </c>
       <c r="R6" t="n">
-        <v>6698527</v>
+        <v>6698275</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,12 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125495484</v>
+        <v>125495038</v>
       </c>
       <c r="B7" t="n">
-        <v>91184</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,35 +1275,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1332,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501295</v>
+        <v>501202</v>
       </c>
       <c r="R7" t="n">
-        <v>6698542</v>
+        <v>6698589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1380,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125492793</v>
+        <v>125494284</v>
       </c>
       <c r="B8" t="n">
         <v>78947</v>
@@ -1440,14 +1416,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blånk, Blånk, Dlr</t>
+          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501287</v>
+        <v>501195</v>
       </c>
       <c r="R8" t="n">
-        <v>6698230</v>
+        <v>6698498</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1643,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125493235</v>
+        <v>125494588</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,38 +1631,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blånk, Blånk, Dlr</t>
+          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501131</v>
+        <v>501130</v>
       </c>
       <c r="R10" t="n">
-        <v>6698334</v>
+        <v>6698527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125497991</v>
+        <v>125494917</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,38 +1753,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blånk, Blånk, Dlr</t>
+          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501259</v>
+        <v>501144</v>
       </c>
       <c r="R11" t="n">
-        <v>6698275</v>
+        <v>6698592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -675,50 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125492793</v>
+        <v>125494917</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blånk, Blånk, Dlr</t>
+          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501287</v>
+        <v>501144</v>
       </c>
       <c r="R2" t="n">
-        <v>6698230</v>
+        <v>6698592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +799,7 @@
         <v>125495484</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,64 +912,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125493171</v>
+        <v>125492793</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501140</v>
+        <v>501287</v>
       </c>
       <c r="R4" t="n">
-        <v>6698315</v>
+        <v>6698230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +992,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,50 +1024,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125493235</v>
+        <v>125497046</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501131</v>
+        <v>501323</v>
       </c>
       <c r="R5" t="n">
-        <v>6698334</v>
+        <v>6698299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1109,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,15 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125497991</v>
+        <v>125494588</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,34 +1152,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blånk, Blånk, Dlr</t>
+          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501259</v>
+        <v>501130</v>
       </c>
       <c r="R6" t="n">
-        <v>6698275</v>
+        <v>6698527</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1226,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,55 +1258,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125495038</v>
+        <v>125497991</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
+          <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501202</v>
+        <v>501259</v>
       </c>
       <c r="R7" t="n">
-        <v>6698589</v>
+        <v>6698275</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,50 +1365,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125494284</v>
+        <v>125493171</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
+          <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501195</v>
+        <v>501140</v>
       </c>
       <c r="R8" t="n">
-        <v>6698498</v>
+        <v>6698315</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,55 +1486,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125497046</v>
+        <v>125493235</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501323</v>
+        <v>501131</v>
       </c>
       <c r="R9" t="n">
-        <v>6698299</v>
+        <v>6698334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,15 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125494588</v>
+        <v>125494284</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,39 +1604,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501130</v>
+        <v>501195</v>
       </c>
       <c r="R10" t="n">
-        <v>6698527</v>
+        <v>6698498</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1714,7 +1678,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,52 +1705,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125494917</v>
+        <v>125495038</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1795,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501144</v>
+        <v>501202</v>
       </c>
       <c r="R11" t="n">
-        <v>6698592</v>
+        <v>6698589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125494917</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125495484</v>
       </c>
       <c r="B3" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>125497991</v>
       </c>
       <c r="B7" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>125493171</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125493235</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125494917</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125495484</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>125492793</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>125497991</v>
       </c>
       <c r="B7" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125493171</v>
+        <v>125493235</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,31 +1393,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501140</v>
+        <v>501131</v>
       </c>
       <c r="R8" t="n">
-        <v>6698315</v>
+        <v>6698334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125493235</v>
+        <v>125493171</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,17 +1500,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501131</v>
+        <v>501140</v>
       </c>
       <c r="R9" t="n">
-        <v>6698334</v>
+        <v>6698315</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
         <v>125494284</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125493235</v>
+        <v>125493171</v>
       </c>
       <c r="B8" t="n">
         <v>98334</v>
@@ -1393,17 +1393,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501131</v>
+        <v>501140</v>
       </c>
       <c r="R8" t="n">
-        <v>6698334</v>
+        <v>6698315</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125493171</v>
+        <v>125493235</v>
       </c>
       <c r="B9" t="n">
         <v>98334</v>
@@ -1500,31 +1514,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501140</v>
+        <v>501131</v>
       </c>
       <c r="R9" t="n">
-        <v>6698315</v>
+        <v>6698334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125494917</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125495484</v>
       </c>
       <c r="B3" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>125492793</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>125497991</v>
       </c>
       <c r="B7" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>125493171</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125493235</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,45 +1593,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125494284</v>
+        <v>125495038</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>8447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501195</v>
+        <v>501202</v>
       </c>
       <c r="R10" t="n">
-        <v>6698498</v>
+        <v>6698589</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,11 +1679,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,50 +1705,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125495038</v>
+        <v>125494284</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501202</v>
+        <v>501195</v>
       </c>
       <c r="R11" t="n">
-        <v>6698589</v>
+        <v>6698498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,6 +1786,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125494917</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>125493171</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125493235</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,50 +1593,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125495038</v>
+        <v>125494284</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501202</v>
+        <v>501195</v>
       </c>
       <c r="R10" t="n">
-        <v>6698589</v>
+        <v>6698498</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,6 +1674,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,45 +1705,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125494284</v>
+        <v>125495038</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501195</v>
+        <v>501202</v>
       </c>
       <c r="R11" t="n">
-        <v>6698498</v>
+        <v>6698589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,11 +1791,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125492793</v>
+        <v>125497046</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +923,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501287</v>
+        <v>501323</v>
       </c>
       <c r="R4" t="n">
-        <v>6698230</v>
+        <v>6698299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125497046</v>
+        <v>125492793</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,39 +1040,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501323</v>
+        <v>501287</v>
       </c>
       <c r="R5" t="n">
-        <v>6698299</v>
+        <v>6698230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125497046</v>
+        <v>125492793</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,39 +923,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501323</v>
+        <v>501287</v>
       </c>
       <c r="R4" t="n">
-        <v>6698299</v>
+        <v>6698230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +992,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125492793</v>
+        <v>125497046</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,34 +1035,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501287</v>
+        <v>501323</v>
       </c>
       <c r="R5" t="n">
-        <v>6698230</v>
+        <v>6698299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1593,45 +1593,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125494284</v>
+        <v>125495038</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501195</v>
+        <v>501202</v>
       </c>
       <c r="R10" t="n">
-        <v>6698498</v>
+        <v>6698589</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,11 +1679,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,50 +1705,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125495038</v>
+        <v>125494284</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501202</v>
+        <v>501195</v>
       </c>
       <c r="R11" t="n">
-        <v>6698589</v>
+        <v>6698498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,6 +1786,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125494917</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125495484</v>
       </c>
       <c r="B3" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>125492793</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>125497046</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>125494588</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>125497991</v>
       </c>
       <c r="B7" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>125493171</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125493235</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,50 +1593,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125495038</v>
+        <v>125494284</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501202</v>
+        <v>501195</v>
       </c>
       <c r="R10" t="n">
-        <v>6698589</v>
+        <v>6698498</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,6 +1674,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,45 +1705,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125494284</v>
+        <v>125495038</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flomyrans naturreservat, Flomyrans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501195</v>
+        <v>501202</v>
       </c>
       <c r="R11" t="n">
-        <v>6698498</v>
+        <v>6698589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,11 +1791,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125492793</v>
+        <v>125497046</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +923,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501287</v>
+        <v>501323</v>
       </c>
       <c r="R4" t="n">
-        <v>6698230</v>
+        <v>6698299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125497046</v>
+        <v>125492793</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,39 +1040,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501323</v>
+        <v>501287</v>
       </c>
       <c r="R5" t="n">
-        <v>6698299</v>
+        <v>6698230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125494917</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>125495484</v>
       </c>
       <c r="B3" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125497046</v>
+        <v>125492793</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,39 +923,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501323</v>
+        <v>501287</v>
       </c>
       <c r="R4" t="n">
-        <v>6698299</v>
+        <v>6698230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +992,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125492793</v>
+        <v>125497046</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,34 +1035,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blånk, Blånk, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501287</v>
+        <v>501323</v>
       </c>
       <c r="R5" t="n">
-        <v>6698230</v>
+        <v>6698299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1261,7 +1261,7 @@
         <v>125497991</v>
       </c>
       <c r="B7" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>125493171</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>125493235</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,6 +1815,580 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127709661</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Överbacka 5:8 Garnlav, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>501256</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6698293</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127709346</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>500975</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6698590</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127709480</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>501252</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6698490</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127709846</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91505</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Överbacka Violmussling, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>501307</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6698260</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127709572</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Överbacka 5:8 Fläcknycklar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>501237</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6698330</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>127709661</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,64 +1924,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R13" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,11 +2007,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2039,6 +2015,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2055,45 +2046,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R14" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,6 +2148,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2146,21 +2161,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91505</v>
+        <v>91507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1924,45 +1924,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B13" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R13" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,6 +2026,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2015,21 +2039,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2046,64 +2055,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R14" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,11 +2138,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2161,6 +2146,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1924,64 +1924,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R13" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,11 +2007,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2039,6 +2015,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2055,45 +2046,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R14" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,6 +2148,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2146,21 +2161,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91507</v>
+        <v>91513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>127709661</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>127709661</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91516</v>
+        <v>91524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1924,45 +1924,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B13" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R13" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,6 +2026,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2015,21 +2039,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2046,64 +2055,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R14" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,11 +2138,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2161,6 +2146,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91524</v>
+        <v>91525</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1924,64 +1924,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R13" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,11 +2007,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2039,6 +2015,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2055,45 +2046,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R14" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,6 +2148,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2146,21 +2161,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91525</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1924,45 +1924,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R13" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,6 +2026,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2015,21 +2039,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2046,64 +2055,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R14" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,11 +2138,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2161,6 +2146,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>127709661</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,64 +1924,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>91360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R13" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,11 +2007,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2039,6 +2015,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2055,45 +2046,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R14" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,6 +2148,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2146,21 +2161,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91527</v>
+        <v>91535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1924,45 +1924,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B13" t="n">
-        <v>91360</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R13" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,6 +2026,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2015,21 +2039,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2046,64 +2055,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B14" t="n">
-        <v>98478</v>
+        <v>91360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R14" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,11 +2138,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2161,6 +2146,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 21827-2025 artfynd.xlsx
+++ b/artfynd/A 21827-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>127709661</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,64 +1924,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709346</v>
+        <v>127709480</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>91371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
+          <t>Överbacka 5:8 Ullticka, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500975</v>
+        <v>501252</v>
       </c>
       <c r="R13" t="n">
-        <v>6698590</v>
+        <v>6698490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,11 +2007,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2039,6 +2015,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2055,45 +2046,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709480</v>
+        <v>127709346</v>
       </c>
       <c r="B14" t="n">
-        <v>91360</v>
+        <v>98490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överbacka 5:8 Ullticka, Dlr</t>
+          <t>Gagnef Överbacka 5:8 Söder vändplan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501252</v>
+        <v>500975</v>
       </c>
       <c r="R14" t="n">
-        <v>6698490</v>
+        <v>6698590</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,6 +2148,11 @@
           <t>20:43</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Litet bestånd i den sparade skogen som omges av hygge</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2146,21 +2161,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2180,7 +2180,7 @@
         <v>127709846</v>
       </c>
       <c r="B15" t="n">
-        <v>91535</v>
+        <v>91546</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>127709572</v>
       </c>
       <c r="B16" t="n">
-        <v>98395</v>
+        <v>98407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
